--- a/data/input/reel_player_data_pipeline_v1.xlsx
+++ b/data/input/reel_player_data_pipeline_v1.xlsx
@@ -526,12 +526,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,36 +616,21 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -784,45 +769,21 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -973,47 +934,21 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1140,32 +1075,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>